--- a/data_fetching/Entsoe/Border_Flows.xlsx
+++ b/data_fetching/Entsoe/Border_Flows.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_83FE812D3FE8515DB03C348050B35F5635147428" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B04D6881-8A7B-4923-B545-2C0807D371A6}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -61,11 +80,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,13 +148,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -173,7 +200,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -207,6 +234,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -241,9 +269,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -416,11 +445,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N101"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -464,9 +509,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>46022.95833333334</v>
+        <v>46022.958333333343</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -508,7 +553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46022.96875</v>
       </c>
@@ -552,9 +597,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>46022.97916666666</v>
+        <v>46022.979166666657</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -596,9 +641,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>46022.98958333334</v>
+        <v>46022.989583333343</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -640,7 +685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46023</v>
       </c>
@@ -684,9 +729,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>46023.01041666666</v>
+        <v>46023.010416666657</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -728,9 +773,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>46023.02083333334</v>
+        <v>46023.020833333343</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -772,7 +817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46023.03125</v>
       </c>
@@ -816,9 +861,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>46023.04166666666</v>
+        <v>46023.041666666657</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -860,9 +905,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>46023.05208333334</v>
+        <v>46023.052083333343</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -904,7 +949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46023.0625</v>
       </c>
@@ -948,9 +993,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>46023.07291666666</v>
+        <v>46023.072916666657</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -992,9 +1037,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>46023.08333333334</v>
+        <v>46023.083333333343</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1036,7 +1081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>46023.09375</v>
       </c>
@@ -1080,9 +1125,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>46023.10416666666</v>
+        <v>46023.104166666657</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1124,9 +1169,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>46023.11458333334</v>
+        <v>46023.114583333343</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1168,7 +1213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>46023.125</v>
       </c>
@@ -1212,9 +1257,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46023.13541666666</v>
+        <v>46023.135416666657</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1256,9 +1301,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>46023.14583333334</v>
+        <v>46023.145833333343</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1300,7 +1345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>46023.15625</v>
       </c>
@@ -1344,9 +1389,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>46023.16666666666</v>
+        <v>46023.166666666657</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1388,9 +1433,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>46023.17708333334</v>
+        <v>46023.177083333343</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1432,7 +1477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>46023.1875</v>
       </c>
@@ -1476,9 +1521,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>46023.19791666666</v>
+        <v>46023.197916666657</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1520,9 +1565,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>46023.20833333334</v>
+        <v>46023.208333333343</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1564,7 +1609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>46023.21875</v>
       </c>
@@ -1608,9 +1653,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>46023.22916666666</v>
+        <v>46023.229166666657</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1652,9 +1697,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>46023.23958333334</v>
+        <v>46023.239583333343</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1696,7 +1741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>46023.25</v>
       </c>
@@ -1740,9 +1785,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>46023.26041666666</v>
+        <v>46023.260416666657</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1784,9 +1829,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>46023.27083333334</v>
+        <v>46023.270833333343</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1828,7 +1873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>46023.28125</v>
       </c>
@@ -1872,9 +1917,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>46023.29166666666</v>
+        <v>46023.291666666657</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1916,9 +1961,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>46023.30208333334</v>
+        <v>46023.302083333343</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1960,7 +2005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>46023.3125</v>
       </c>
@@ -2004,9 +2049,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>46023.32291666666</v>
+        <v>46023.322916666657</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2048,12 +2093,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>46023.33333333334</v>
+        <v>46023.333333333343</v>
       </c>
       <c r="B38">
-        <v>601.6600000000001</v>
+        <v>601.66000000000008</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2083,21 +2128,21 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>816.6600000000001</v>
+        <v>816.66000000000008</v>
       </c>
       <c r="M38">
         <v>0</v>
       </c>
       <c r="N38">
-        <v>816.6600000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+        <v>816.66000000000008</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>46023.34375</v>
       </c>
       <c r="B39">
-        <v>601.6600000000001</v>
+        <v>601.66000000000008</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2127,21 +2172,21 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>816.6600000000001</v>
+        <v>816.66000000000008</v>
       </c>
       <c r="M39">
         <v>0</v>
       </c>
       <c r="N39">
-        <v>816.6600000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+        <v>816.66000000000008</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>46023.35416666666</v>
+        <v>46023.354166666657</v>
       </c>
       <c r="B40">
-        <v>601.6600000000001</v>
+        <v>601.66000000000008</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -2171,21 +2216,21 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>816.6600000000001</v>
+        <v>816.66000000000008</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40">
-        <v>816.6600000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+        <v>816.66000000000008</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>46023.36458333334</v>
+        <v>46023.364583333343</v>
       </c>
       <c r="B41">
-        <v>601.6600000000001</v>
+        <v>601.66000000000008</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2215,16 +2260,16 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>2992.207</v>
+        <v>2992.2069999999999</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
       <c r="N41">
-        <v>2992.207</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+        <v>2992.2069999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>46023.375</v>
       </c>
@@ -2241,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <v>2045.178</v>
+        <v>2045.1780000000001</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -2259,18 +2304,18 @@
         <v>33.75</v>
       </c>
       <c r="L42">
-        <v>3151.218</v>
+        <v>3151.2179999999998</v>
       </c>
       <c r="M42">
         <v>33.75</v>
       </c>
       <c r="N42">
-        <v>3117.468</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
+        <v>3117.4679999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>46023.38541666666</v>
+        <v>46023.385416666657</v>
       </c>
       <c r="B43">
         <v>1106.04</v>
@@ -2285,7 +2330,7 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>2350.139</v>
+        <v>2350.1390000000001</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -2303,18 +2348,18 @@
         <v>33.75</v>
       </c>
       <c r="L43">
-        <v>3456.179</v>
+        <v>3456.1790000000001</v>
       </c>
       <c r="M43">
         <v>33.75</v>
       </c>
       <c r="N43">
-        <v>3422.429</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
+        <v>3422.4290000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>46023.39583333334</v>
+        <v>46023.395833333343</v>
       </c>
       <c r="B44">
         <v>1106.04</v>
@@ -2356,7 +2401,7 @@
         <v>1072.29</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>46023.40625</v>
       </c>
@@ -2400,9 +2445,9 @@
         <v>1072.29</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>46023.41666666666</v>
+        <v>46023.416666666657</v>
       </c>
       <c r="B46">
         <v>645.16</v>
@@ -2444,9 +2489,9 @@
         <v>645.16</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>46023.42708333334</v>
+        <v>46023.427083333343</v>
       </c>
       <c r="B47">
         <v>645.16</v>
@@ -2488,7 +2533,7 @@
         <v>645.16</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>46023.4375</v>
       </c>
@@ -2532,9 +2577,9 @@
         <v>645.16</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>46023.44791666666</v>
+        <v>46023.447916666657</v>
       </c>
       <c r="B49">
         <v>645.16</v>
@@ -2576,9 +2621,9 @@
         <v>645.16</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>46023.45833333334</v>
+        <v>46023.458333333343</v>
       </c>
       <c r="B50">
         <v>486</v>
@@ -2593,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>1952.505</v>
+        <v>1952.5050000000001</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -2611,16 +2656,16 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>2438.505</v>
+        <v>2438.5050000000001</v>
       </c>
       <c r="M50">
         <v>0</v>
       </c>
       <c r="N50">
-        <v>2438.505</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
+        <v>2438.5050000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>46023.46875</v>
       </c>
@@ -2664,9 +2709,9 @@
         <v>2359.277</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>46023.47916666666</v>
+        <v>46023.479166666657</v>
       </c>
       <c r="B52">
         <v>486</v>
@@ -2681,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <v>1923.469</v>
+        <v>1923.4690000000001</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2699,18 +2744,18 @@
         <v>0</v>
       </c>
       <c r="L52">
-        <v>2409.469</v>
+        <v>2409.4690000000001</v>
       </c>
       <c r="M52">
         <v>0</v>
       </c>
       <c r="N52">
-        <v>2409.469</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
+        <v>2409.4690000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>46023.48958333334</v>
+        <v>46023.489583333343</v>
       </c>
       <c r="B53">
         <v>486</v>
@@ -2725,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>1940.766</v>
+        <v>1940.7660000000001</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2743,21 +2788,21 @@
         <v>0</v>
       </c>
       <c r="L53">
-        <v>2426.766</v>
+        <v>2426.7660000000001</v>
       </c>
       <c r="M53">
         <v>0</v>
       </c>
       <c r="N53">
-        <v>2426.766</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
+        <v>2426.7660000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>46023.5</v>
       </c>
       <c r="B54">
-        <v>426.1199999999999</v>
+        <v>426.11999999999989</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2769,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="F54">
-        <v>1916.253</v>
+        <v>1916.2529999999999</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -2796,12 +2841,12 @@
         <v>2481.123</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>46023.51041666666</v>
+        <v>46023.510416666657</v>
       </c>
       <c r="B55">
-        <v>426.1199999999999</v>
+        <v>426.11999999999989</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -2813,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="F55">
-        <v>1861.456</v>
+        <v>1861.4559999999999</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -2840,12 +2885,12 @@
         <v>2426.326</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>46023.52083333334</v>
+        <v>46023.520833333343</v>
       </c>
       <c r="B56">
-        <v>426.1199999999999</v>
+        <v>426.11999999999989</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2875,21 +2920,21 @@
         <v>0</v>
       </c>
       <c r="L56">
-        <v>2547.427</v>
+        <v>2547.4270000000001</v>
       </c>
       <c r="M56">
         <v>0</v>
       </c>
       <c r="N56">
-        <v>2547.427</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
+        <v>2547.4270000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>46023.53125</v>
       </c>
       <c r="B57">
-        <v>426.1199999999999</v>
+        <v>426.11999999999989</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2901,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="F57">
-        <v>1817.427</v>
+        <v>1817.4269999999999</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -2928,9 +2973,9 @@
         <v>2382.297</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>46023.54166666666</v>
+        <v>46023.541666666657</v>
       </c>
       <c r="B58">
         <v>256.74</v>
@@ -2972,9 +3017,9 @@
         <v>537.99</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>46023.55208333334</v>
+        <v>46023.552083333343</v>
       </c>
       <c r="B59">
         <v>256.74</v>
@@ -3016,7 +3061,7 @@
         <v>537.99</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>46023.5625</v>
       </c>
@@ -3060,9 +3105,9 @@
         <v>537.99</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>46023.57291666666</v>
+        <v>46023.572916666657</v>
       </c>
       <c r="B61">
         <v>256.74</v>
@@ -3104,15 +3149,15 @@
         <v>537.99</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>46023.58333333334</v>
+        <v>46023.583333333343</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
-        <v>199.7199999999999</v>
+        <v>199.71999999999991</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -3142,13 +3187,13 @@
         <v>0</v>
       </c>
       <c r="M62">
-        <v>199.7199999999999</v>
+        <v>199.71999999999991</v>
       </c>
       <c r="N62">
-        <v>-199.7199999999999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14">
+        <v>-199.71999999999991</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>46023.59375</v>
       </c>
@@ -3156,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="C63">
-        <v>199.7199999999999</v>
+        <v>199.71999999999991</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -3186,21 +3231,21 @@
         <v>0</v>
       </c>
       <c r="M63">
-        <v>199.7199999999999</v>
+        <v>199.71999999999991</v>
       </c>
       <c r="N63">
-        <v>-199.7199999999999</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
+        <v>-199.71999999999991</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>46023.60416666666</v>
+        <v>46023.604166666657</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64">
-        <v>199.7199999999999</v>
+        <v>199.71999999999991</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -3230,21 +3275,21 @@
         <v>0</v>
       </c>
       <c r="M64">
-        <v>199.7199999999999</v>
+        <v>199.71999999999991</v>
       </c>
       <c r="N64">
-        <v>-199.7199999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14">
+        <v>-199.71999999999991</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>46023.61458333334</v>
+        <v>46023.614583333343</v>
       </c>
       <c r="B65">
         <v>0</v>
       </c>
       <c r="C65">
-        <v>199.7199999999999</v>
+        <v>199.71999999999991</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -3274,13 +3319,13 @@
         <v>0</v>
       </c>
       <c r="M65">
-        <v>199.7199999999999</v>
+        <v>199.71999999999991</v>
       </c>
       <c r="N65">
-        <v>-199.7199999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14">
+        <v>-199.71999999999991</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>46023.625</v>
       </c>
@@ -3288,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="C66">
-        <v>222.8200000000002</v>
+        <v>222.82000000000019</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -3318,21 +3363,21 @@
         <v>0</v>
       </c>
       <c r="M66">
-        <v>222.8200000000002</v>
+        <v>222.82000000000019</v>
       </c>
       <c r="N66">
-        <v>-222.8200000000002</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14">
+        <v>-222.82000000000019</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>46023.63541666666</v>
+        <v>46023.635416666657</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>222.8200000000002</v>
+        <v>222.82000000000019</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -3362,21 +3407,21 @@
         <v>0</v>
       </c>
       <c r="M67">
-        <v>222.8200000000002</v>
+        <v>222.82000000000019</v>
       </c>
       <c r="N67">
-        <v>-222.8200000000002</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14">
+        <v>-222.82000000000019</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>46023.64583333334</v>
+        <v>46023.645833333343</v>
       </c>
       <c r="B68">
         <v>0</v>
       </c>
       <c r="C68">
-        <v>222.8200000000002</v>
+        <v>222.82000000000019</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3406,13 +3451,13 @@
         <v>0</v>
       </c>
       <c r="M68">
-        <v>222.8200000000002</v>
+        <v>222.82000000000019</v>
       </c>
       <c r="N68">
-        <v>-222.8200000000002</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14">
+        <v>-222.82000000000019</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>46023.65625</v>
       </c>
@@ -3420,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="C69">
-        <v>222.8200000000002</v>
+        <v>222.82000000000019</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -3450,15 +3495,15 @@
         <v>0</v>
       </c>
       <c r="M69">
-        <v>222.8200000000002</v>
+        <v>222.82000000000019</v>
       </c>
       <c r="N69">
-        <v>-222.8200000000002</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14">
+        <v>-222.82000000000019</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>46023.66666666666</v>
+        <v>46023.666666666657</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -3500,9 +3545,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>46023.67708333334</v>
+        <v>46023.677083333343</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -3544,7 +3589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>46023.6875</v>
       </c>
@@ -3588,9 +3633,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>46023.69791666666</v>
+        <v>46023.697916666657</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -3632,9 +3677,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>46023.70833333334</v>
+        <v>46023.708333333343</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -3676,7 +3721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>46023.71875</v>
       </c>
@@ -3720,9 +3765,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>46023.72916666666</v>
+        <v>46023.729166666657</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -3764,9 +3809,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>46023.73958333334</v>
+        <v>46023.739583333343</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -3808,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>46023.75</v>
       </c>
@@ -3852,9 +3897,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>46023.76041666666</v>
+        <v>46023.760416666657</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -3896,9 +3941,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>46023.77083333334</v>
+        <v>46023.770833333343</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -3940,7 +3985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>46023.78125</v>
       </c>
@@ -3984,9 +4029,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>46023.79166666666</v>
+        <v>46023.791666666657</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -4028,9 +4073,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>46023.80208333334</v>
+        <v>46023.802083333343</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -4072,7 +4117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>46023.8125</v>
       </c>
@@ -4116,9 +4161,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>46023.82291666666</v>
+        <v>46023.822916666657</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -4160,9 +4205,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>46023.83333333334</v>
+        <v>46023.833333333343</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -4204,7 +4249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>46023.84375</v>
       </c>
@@ -4248,9 +4293,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>46023.85416666666</v>
+        <v>46023.854166666657</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -4292,9 +4337,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>46023.86458333334</v>
+        <v>46023.864583333343</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -4336,7 +4381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>46023.875</v>
       </c>
@@ -4380,9 +4425,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>46023.88541666666</v>
+        <v>46023.885416666657</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -4424,9 +4469,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>46023.89583333334</v>
+        <v>46023.895833333343</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -4468,7 +4513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>46023.90625</v>
       </c>
@@ -4512,9 +4557,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <v>46023.91666666666</v>
+        <v>46023.916666666657</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -4556,9 +4601,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>46023.92708333334</v>
+        <v>46023.927083333343</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -4600,7 +4645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>46023.9375</v>
       </c>
@@ -4644,9 +4689,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <v>46023.94791666666</v>
+        <v>46023.947916666657</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -4688,9 +4733,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <v>46023.95833333334</v>
+        <v>46023.958333333343</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -4732,7 +4777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>46023.96875</v>
       </c>
@@ -4776,9 +4821,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <v>46023.97916666666</v>
+        <v>46023.979166666657</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -4820,9 +4865,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
-        <v>46023.98958333334</v>
+        <v>46023.989583333343</v>
       </c>
       <c r="B101">
         <v>0</v>
